--- a/data/metas.xlsx
+++ b/data/metas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/09 Septiembre/Liquidacióncvs -septiembre/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1094" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C932EF8-69D7-4753-A4A5-84D2A28B092D}"/>
+  <xr:revisionPtr revIDLastSave="1107" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C322DB8-2A59-4E12-97F5-2B1BE27882F4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1391136-BBFC-43C7-B899-B77B0ECC5956}"/>
   </bookViews>
@@ -159,6 +159,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="168" formatCode="&quot;$&quot;\ #,##0"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -196,7 +199,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -205,6 +208,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2700,8 +2706,8 @@
       <c r="C127" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D127" s="2">
-        <v>8000000</v>
+      <c r="D127" s="4">
+        <v>8500000</v>
       </c>
       <c r="E127" s="2">
         <v>2400</v>
@@ -2717,7 +2723,7 @@
       <c r="C128" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D128" s="2">
+      <c r="D128" s="4">
         <v>2500000</v>
       </c>
       <c r="E128" s="2">
@@ -2734,8 +2740,8 @@
       <c r="C129" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D129" s="2">
-        <v>5500000</v>
+      <c r="D129" s="4">
+        <v>6000000</v>
       </c>
       <c r="E129" s="2">
         <v>1500</v>
@@ -2751,7 +2757,7 @@
       <c r="C130" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D130" s="2">
+      <c r="D130" s="4">
         <v>3000000</v>
       </c>
       <c r="E130" s="2">
@@ -2768,7 +2774,7 @@
       <c r="C131" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D131" s="2">
+      <c r="D131" s="4">
         <v>5000000</v>
       </c>
       <c r="E131" s="2">
@@ -2785,7 +2791,7 @@
       <c r="C132" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D132" s="2">
+      <c r="D132" s="4">
         <v>7500000</v>
       </c>
       <c r="E132" s="2">
@@ -2802,7 +2808,7 @@
       <c r="C133" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D133" s="2">
+      <c r="D133" s="4">
         <v>8000000</v>
       </c>
       <c r="E133" s="2">
@@ -2819,7 +2825,7 @@
       <c r="C134" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D134" s="2">
+      <c r="D134" s="4">
         <v>5500000</v>
       </c>
       <c r="E134" s="2">
@@ -2836,7 +2842,7 @@
       <c r="C135" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D135" s="2">
+      <c r="D135" s="4">
         <v>2500000</v>
       </c>
       <c r="E135" s="2">
@@ -2853,7 +2859,7 @@
       <c r="C136" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D136" s="2">
+      <c r="D136" s="4">
         <v>4000000</v>
       </c>
       <c r="E136" s="2">
@@ -2870,7 +2876,7 @@
       <c r="C137" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D137" s="2">
+      <c r="D137" s="4">
         <v>2000000</v>
       </c>
       <c r="E137" s="2">
@@ -2887,7 +2893,7 @@
       <c r="C138" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D138" s="2">
+      <c r="D138" s="4">
         <v>5000000</v>
       </c>
       <c r="E138" s="2">
@@ -2904,8 +2910,8 @@
       <c r="C139" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D139" s="2">
-        <v>3000000</v>
+      <c r="D139" s="4">
+        <v>2500000</v>
       </c>
       <c r="E139" s="2">
         <v>1800</v>
@@ -2921,7 +2927,7 @@
       <c r="C140" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D140" s="2">
+      <c r="D140" s="4">
         <v>6000000</v>
       </c>
       <c r="E140" s="2">
@@ -2938,7 +2944,7 @@
       <c r="C141" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D141" s="2">
+      <c r="D141" s="4">
         <v>4000000</v>
       </c>
       <c r="E141" s="2">
@@ -2955,7 +2961,7 @@
       <c r="C142" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D142" s="2">
+      <c r="D142" s="4">
         <v>4500000</v>
       </c>
       <c r="E142" s="2">
@@ -2972,7 +2978,7 @@
       <c r="C143" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D143" s="2">
+      <c r="D143" s="4">
         <v>3000000</v>
       </c>
       <c r="E143" s="2">
@@ -2989,7 +2995,7 @@
       <c r="C144" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D144" s="2">
+      <c r="D144" s="4">
         <v>7000000</v>
       </c>
       <c r="E144" s="2">
@@ -3006,7 +3012,7 @@
       <c r="C145" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D145" s="2">
+      <c r="D145" s="4">
         <v>4000000</v>
       </c>
       <c r="E145" s="2">
@@ -3023,8 +3029,8 @@
       <c r="C146" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D146" s="2">
-        <v>5500000</v>
+      <c r="D146" s="4">
+        <v>5000000</v>
       </c>
       <c r="E146" s="2">
         <v>2200</v>
@@ -3040,8 +3046,8 @@
       <c r="C147" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D147" s="2">
-        <v>3000000</v>
+      <c r="D147" s="4">
+        <v>2500000</v>
       </c>
       <c r="E147" s="2">
         <v>1000</v>
@@ -3057,8 +3063,8 @@
       <c r="C148" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D148" s="2">
-        <v>117000000</v>
+      <c r="D148" s="4">
+        <v>118000000</v>
       </c>
       <c r="E148" s="2">
         <v>55000</v>
@@ -3074,8 +3080,8 @@
       <c r="C149" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D149" s="2">
-        <v>10000</v>
+      <c r="D149" s="4">
+        <v>100000</v>
       </c>
       <c r="E149" s="2">
         <v>54450</v>
@@ -3176,7 +3182,7 @@
       <c r="C155" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D155" s="2">
+      <c r="D155" s="4">
         <v>2000000</v>
       </c>
       <c r="E155" s="2">

--- a/data/metas.xlsx
+++ b/data/metas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/09 Septiembre/Liquidacióncvs -septiembre/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1107" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C322DB8-2A59-4E12-97F5-2B1BE27882F4}"/>
+  <xr:revisionPtr revIDLastSave="1117" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C7626C3-D098-4632-B1D2-497C467278C4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1391136-BBFC-43C7-B899-B77B0ECC5956}"/>
   </bookViews>
@@ -160,7 +160,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -208,7 +208,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -922,7 +922,7 @@
         <v>22</v>
       </c>
       <c r="D22" s="2">
-        <v>1200</v>
+        <v>46</v>
       </c>
       <c r="E22" s="2">
         <v>1450</v>
@@ -1092,7 +1092,7 @@
         <v>22</v>
       </c>
       <c r="D32" s="2">
-        <v>1500</v>
+        <v>1212</v>
       </c>
       <c r="E32" s="2">
         <v>3500</v>
@@ -1517,7 +1517,7 @@
         <v>22</v>
       </c>
       <c r="D57" s="2">
-        <v>1200</v>
+        <v>1062</v>
       </c>
       <c r="E57" s="2">
         <v>1100</v>
@@ -1687,7 +1687,7 @@
         <v>22</v>
       </c>
       <c r="D67" s="2">
-        <v>1200</v>
+        <v>1062</v>
       </c>
       <c r="E67" s="2">
         <v>1800</v>
@@ -1942,7 +1942,7 @@
         <v>22</v>
       </c>
       <c r="D82" s="2">
-        <v>1500</v>
+        <v>1385</v>
       </c>
       <c r="E82" s="2">
         <v>3700</v>
@@ -2282,7 +2282,7 @@
         <v>22</v>
       </c>
       <c r="D102" s="2">
-        <v>1500</v>
+        <v>1154</v>
       </c>
       <c r="E102" s="2">
         <v>2600</v>
@@ -2537,7 +2537,7 @@
         <v>22</v>
       </c>
       <c r="D117" s="2">
-        <v>27700</v>
+        <v>25521</v>
       </c>
       <c r="E117" s="2">
         <v>55000</v>
@@ -2622,7 +2622,7 @@
         <v>22</v>
       </c>
       <c r="D122" s="2">
-        <v>27700</v>
+        <v>0</v>
       </c>
       <c r="E122" s="2">
         <v>54450</v>

--- a/data/metas.xlsx
+++ b/data/metas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/09 Septiembre/Liquidacióncvs -septiembre/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1117" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C7626C3-D098-4632-B1D2-497C467278C4}"/>
+  <xr:revisionPtr revIDLastSave="1119" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA0FC3AB-73B8-43B6-BF06-9C39EE884A8A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1391136-BBFC-43C7-B899-B77B0ECC5956}"/>
   </bookViews>
